--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -432,6 +432,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jan 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feb 2026</t>
   </si>
 </sst>
 </file>
@@ -3877,6 +3880,29 @@
         <v>-0.00725087992176722</v>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>140</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.0177914110429449</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.0104660929315991</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.00487677541890053</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.00443365158709515</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.00421501561288207</v>
+      </c>
+      <c r="G135" t="n">
+        <v>-0.00620012450753198</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t xml:space="preserve">Feb 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mar 2026</t>
   </si>
 </sst>
 </file>
@@ -3903,6 +3906,29 @@
         <v>-0.00620012450753198</v>
       </c>
     </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>141</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.0238532110091743</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.00974102855852454</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.00480136925881944</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.00475960174766034</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.00234216604292814</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.0022090454012418</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -438,6 +438,9 @@
   </si>
   <si>
     <t xml:space="preserve">Mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apr 2026</t>
   </si>
 </sst>
 </file>
@@ -3929,6 +3932,29 @@
         <v>0.0022090454012418</v>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>142</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.0281517747858018</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.00443929150665282</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00390270437841743</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.0041383082506227</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00447245127786494</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.0111990193722439</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t xml:space="preserve">Apr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">May 2026</t>
   </si>
 </sst>
 </file>
@@ -3955,6 +3958,29 @@
         <v>0.0111990193722439</v>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>143</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.032258064516129</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.00708769356922802</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.00363172000265537</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.00462127659574468</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.00398918005071847</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.0129281942977825</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -444,6 +444,9 @@
   </si>
   <si>
     <t xml:space="preserve">May 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jun 2026</t>
   </si>
 </sst>
 </file>
@@ -3981,6 +3984,29 @@
         <v>0.0129281942977825</v>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>144</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.0279805352798053</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.00906078524056738</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.00334092310566125</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.0042242063416907</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.00304869388519019</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.00830592670669574</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
